--- a/AAII_Financials/Quarterly/WMMVY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WMMVY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
   <si>
     <t>WMMVY</t>
   </si>
@@ -656,177 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -869,86 +873,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>12395200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10565100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11715600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11250000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12601800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9944600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9521500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9308000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9842500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8170100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8349900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8198300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9216600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7785000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14805300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7576100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8090400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6651000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7862800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7776400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8698500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7080300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7020300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6856800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>8363100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>6736400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,86 +998,89 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>9542400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8060900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8974400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8615500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9677700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7592200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7306800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7139600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7565300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6238700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6446300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6329100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7126800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5950700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>11448100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5853600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6245700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5099100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6076200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>5992600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6786200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>5437300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>5420400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>5285300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>6525500</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>5222300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1113,86 +1123,89 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>2852800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2504200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2741200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2634500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2924100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2352400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2214700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2168400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2277300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1931300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1903600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1869200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2089800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1834400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3357200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1722400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1844700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1551900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1786600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1783700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1912300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1643000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1599900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1571500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1837600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1514100</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,8 +1543,8 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1601,8 +1621,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1645,8 +1668,8 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,8 +1790,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1808,86 +1835,89 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>11332700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9694600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10794200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10295500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11494400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9071300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8777300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8493600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8944900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7489200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7799100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7497800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8412800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7112900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13624100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6960000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7378300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6119400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7303800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7168700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7984100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6538800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6520800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>6345000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>7691500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>6251400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1930,86 +1960,89 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>1062500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>870400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>921400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>954500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1107400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>873300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>744200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>814400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>897700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>680900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>550800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>700500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>803800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>672100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1181200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>616100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>712200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>531600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>559000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>607600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>714500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>541500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>499500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>511900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>671600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>485000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,86 +2130,89 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>45600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>48600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>29900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>16300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>11900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>24200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-103900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>216400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-66900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-50000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-16500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-5300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-9700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>7100</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2218,86 +2255,89 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>1366300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1178500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1236400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1248300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1400200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1143900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1012800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1057900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1142400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>910900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>673300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>909000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1238200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>820800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1483100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>771900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>859000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>654300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>734600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>768700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>866900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>685500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>637700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>651100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>828900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>628000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,48 +2380,48 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>94900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>95000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>104000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>102600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>97600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>90100</v>
-      </c>
-      <c r="W22" s="3">
-        <v>87800</v>
       </c>
       <c r="X22" s="3">
         <v>87800</v>
       </c>
       <c r="Y22" s="3">
+        <v>87800</v>
+      </c>
+      <c r="Z22" s="3">
         <v>80000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>80500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>80600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>74500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>285400</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
@@ -2413,13 +2453,16 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="3">
         <v>20700</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2462,86 +2505,89 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>1013200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>824000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>847300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>859100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1026100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>795100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>680500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>723000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>837800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>609400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>366300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>623500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>734800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>605200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1080700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>566100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>706400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>515100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>569700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>605600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>708200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>536200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>492400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>502100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>657900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>494000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,86 +2630,89 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>240800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>175200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>195000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>193800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>247700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>171000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>148300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>174100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>204900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>156300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>284100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>145100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>177500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>140600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>238300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>133500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>170100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>124400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>143000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>158000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>161000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>122300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>143500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>136900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>158600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>138500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,8 +2833,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2828,86 +2880,89 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>772500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>648800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>652300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>665300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>778400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>624200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>532200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>548900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>632900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>453100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>82100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>478400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>557300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>464600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>842400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>432600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>536300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>390800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>426700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>447600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>547200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>413900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>348900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>365200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>499400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>355500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,86 +3005,89 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>772500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>648800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>652300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>665300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>778400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>624200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>532200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>548900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>632900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>453100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>82100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>478400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>557300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>464600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>842400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>432600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>536300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>390800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>426700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>447600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>547200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>413900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>348900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>365200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>499600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>355400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3194,8 +3255,8 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3258,22 +3319,25 @@
         <v>0</v>
       </c>
       <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3">
         <v>34800</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>348200</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>3600</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>52700</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>178200</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,86 +3630,89 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-45600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-48600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-29900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-16300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-11900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-24200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-20100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>103900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-216400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>66900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>50000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>16500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>6300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>5300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>7000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>9700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3682,86 +3755,89 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>772500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>648800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>652300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>665300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>778400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>624200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>532200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>548900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>632900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>453100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>82100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>478400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>557300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>464600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>842400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>432600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>536300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>390800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>426700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>447600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>547200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>448800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>697100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>368800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>552200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>533600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,8 +3958,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3926,213 +4005,219 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>772500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>648800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>652300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>665300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>778400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>624200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>532200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>548900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>632900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>453100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>82100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>478400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>557300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>464600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>842400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>432600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>536300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>390800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>426700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>447600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>547200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>448800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>697100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>368800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>552200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>533600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1723700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1557900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1588100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1918100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1720400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1171400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1752300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2478500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2655400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2640100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2405600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2871000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2626400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2582500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2471900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2820100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2907600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2098900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2514600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2727700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2278600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1627000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1791400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1894400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1521800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1813000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1531100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1032300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1286800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1473500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1770600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1488100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1622000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1819400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1841000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1367700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>826200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>919400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1485500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>982500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4433,21 +4523,21 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH42" s="3">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI42" s="3">
         <v>7600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>8700</v>
       </c>
-      <c r="AK42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4463,496 +4553,511 @@
       <c r="AP42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1675500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1517800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1479500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1457900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1369700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1300300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1193200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1136000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1133600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1378200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1358100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>906400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>779700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>770100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>871400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>742900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>751900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>937200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>988300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>920500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>792200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>860600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>853400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>654800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>682600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>672500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>680600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>539400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>537800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>565500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>548800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>418800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>462300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>390300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>560400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>393700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>361100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>361800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>715300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>352700</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6153900</v>
+      </c>
+      <c r="E44" s="3">
         <v>5891100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5968400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6173700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5660300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5349100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5312300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5872400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5511300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5731900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5624600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5863300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5190800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5020900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4662700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5314100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5070500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4824900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4717000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4563100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3708200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3651800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3433100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3550500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3193300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3036900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3352000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3446200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2917100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2947500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2888500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2732200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3084200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2919100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3075400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2976400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2675600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2772500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2849600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2843300</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E45" s="3">
         <v>92600</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>98800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>87400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>60900</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>102700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>107900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>57400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>91000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>67000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>48200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>68100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>73600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>44400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>50300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>61500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>46200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>58200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>35200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>64100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>57200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>58600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>88200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>45400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>76000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>60400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>64100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>49800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>66900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>48500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>50800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>39600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>43600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>649000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>667100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>564600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9652100</v>
+      </c>
+      <c r="E46" s="3">
         <v>9059300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9115600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9648500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8837700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7881700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8321400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9589600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9408200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9807600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9448900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9731800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8663900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8416100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8054300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8945300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8803500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7905400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8270200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8272900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6825300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6197600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6113000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6163800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5454800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5581000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5652000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5063300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4817700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5046900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5272000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4696400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5245000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5186000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5527600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4777400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3906500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4702600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5523600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4743100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4995,330 +5100,339 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>120800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>124400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>123600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>129400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>130500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>121700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>110500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>112700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>102600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>111700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>113800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>109100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>91100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>107100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>108800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>107500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>101500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>94300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>99000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>105900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>79200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>73500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>79900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>99800</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15045000</v>
+      </c>
+      <c r="E48" s="3">
         <v>14312500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14365500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13478300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12790300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11865900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11742000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11927900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12207700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13060100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12871900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12116700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11952500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11153500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10874000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10847700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11896800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11839300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11758800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11011700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10426000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10460300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9614800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9590600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9639500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9454700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9350300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9317000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8669300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8851900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6576500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6296400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7530400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7347300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>7245000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>6959000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>6874900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>6833900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>7240200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>6997000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2506600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2482000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2368800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2339500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2322900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2313600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2274400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2263600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2243100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2319800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2267600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2200200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2167000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2164100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2044100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2067600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2181300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2211500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2276300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2211100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2034400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2125400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1885900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2095200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2214900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2189800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1840100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1908900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1796200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1838400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1687100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1686800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2133700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1954500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2036100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1886700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1864000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1933200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2195100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2048200</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>354700</v>
+      </c>
+      <c r="E52" s="3">
         <v>346000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>372300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>368500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>330800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>326300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>324000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>338800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>361000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>397700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>395100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>403000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>421100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>405000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>735100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>766800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>732800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>762700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>726700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>608300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>551900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>519900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>457400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>377700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>361700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>337000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>392400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>419300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>385000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>379800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>340500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>374600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>355100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>385300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>356000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>291600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>265500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>226800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>249600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>197700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28955400</v>
+      </c>
+      <c r="E54" s="3">
         <v>27560000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27510300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27114200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25503900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23465200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23702200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24908200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25035800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26462000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25822100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25330300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24062200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22921700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21828300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22751800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23738100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22848300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23162500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22225700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>19948100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>19416000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18173800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>18339000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17784700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17671700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17325900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16815500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15776900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16224400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13977700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>13148400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15373400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>14972000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>15270600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>13993900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>12984500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>13776500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>15308300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>14051500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6537600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6315600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6882300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6262800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5555100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5300500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5853500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5711400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5880100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6600300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6768600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5969900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5397100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5155000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5223200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5109800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5308900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5132600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5675500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4938300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4254000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4315900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4638100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3945700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3784100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3892600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4322700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3763100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3524800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3632700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3890900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3274300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3722700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3686100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4142700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3310400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2747300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2862000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3500300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2801200</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>314500</v>
+      </c>
+      <c r="E58" s="3">
         <v>295000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>288100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>271600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>260800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>237800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>227200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>233600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>246000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>265200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>255100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>245600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>227200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>192100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>183000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>187200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>212200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>198600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>201900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>196900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>166600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>174600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>161500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>159500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>154900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>145400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>151100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>152200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>144300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>148500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>14100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>13300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>15800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>16800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>19700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>21000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>23100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>26200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>28300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2054700</v>
+      </c>
+      <c r="E59" s="3">
         <v>977300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1445700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2500100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2649600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1002700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1286000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2903100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3002300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1061200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>307500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2820400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2959500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3477400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1770000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3278600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3357600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1480500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1916500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3196000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2912000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2703000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1380900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2449100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2367000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2494300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1158100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1657200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1937600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2485200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1301000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1655600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2137400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2567100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1414400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1668500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1709800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3197300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1479700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1846500</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10010800</v>
+      </c>
+      <c r="E60" s="3">
         <v>8523600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9427000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10160000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9394400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7284000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8196500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9812600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9987000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8753600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9240500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9958600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9341800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9474000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7176200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8575600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8878600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6811700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7794000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8331200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7332600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7193500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6180600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6554300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6306000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6532300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5631800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5572500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5606700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6266300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5205900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4943200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5875900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6270000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5576800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4999800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4480200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>6085500</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>5008300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4678000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4441200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4213200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4202700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4035200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3916800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3660300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3599000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3750500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3947800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4273000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4196300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4058500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4095000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3688100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3457000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3454500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3783700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3711000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3597400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3317600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3167000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3135100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2838500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2830100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2827300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2750300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2687800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2634800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2410800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2439000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>646000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>640200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>772600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>751700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>709900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>694900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>680000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>671600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>694400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>638200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>361300</v>
+      </c>
+      <c r="E62" s="3">
         <v>474200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>340200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>297600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>230300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>209700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>351600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>35500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>642500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>700800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>781200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>866600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>854300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>780000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>720100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>715800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>661600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>694700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>626200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>596100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>662900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>568300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>561300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>574800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>605700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>690200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>740600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>762200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>732800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>853400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>886100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>668600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>736500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>646600</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15299500</v>
+      </c>
+      <c r="E66" s="3">
         <v>13549900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14424800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14932500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13968200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11552900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12526400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14031300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14440900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13619500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14046000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14660900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14088700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13804900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11275600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12730800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13443500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11389300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12245600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12428800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11219800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11044500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9680600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10079100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9759600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9878700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8982600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8775600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8578800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9280100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6457600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6273600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7389100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7783900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7019500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6548100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6046300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7425700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>6439200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>5964300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10307000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10679000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9999200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9082600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8428800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8713700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8035900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7774700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7626500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9909100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8933000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7864300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7189900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6198400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7647400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7042800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7172800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8290000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7477000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6404000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5615700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5083900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5592600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4878800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4426000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4208200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5401600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4939900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4310800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4010800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4771500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4180500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4514300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4089200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4986500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4439600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3991400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3295400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>5291400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4740300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13655900</v>
+      </c>
+      <c r="E76" s="3">
         <v>14010100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13085500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12181700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11535700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11912300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11175800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10876900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10594900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12842400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11776100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10669500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9973400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9116800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10552700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10021000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10294600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11459000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10916900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9796900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8728300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8371500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8493100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8260000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8025100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7793000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8343300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8039900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7198100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6944300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7520100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6874800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7984200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7188100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>8251100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>7445700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6938200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6350800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>8869100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>8087100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,135 +8688,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8670,86 +8865,89 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>772500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>648800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>652300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>665300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>778400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>624200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>532200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>548900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>632900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>453100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>82100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>478400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>557300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>464600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>842400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>432600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>536300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>390800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>426700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>447600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>547200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>448800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>697100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>368800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>552200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>533600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>330200</v>
+      </c>
+      <c r="E83" s="3">
         <v>303400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>233000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>292700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>304100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>329000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>261400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>299800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>293100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>276000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>218800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>241900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>236200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>240200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>258200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>259400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>285100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>286600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>276500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>258700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>244500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>247200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>224600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>221000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>226500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>211000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>217900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>215600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>402300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>205800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>152600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>139200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>164900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>163200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>158700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>149300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>145300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>149000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>150200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1048800</v>
+      </c>
+      <c r="E89" s="3">
         <v>274900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2405900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1200400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1142700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-217400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1867100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>615800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>711100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>523900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2377000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>966500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1248100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>371700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1830100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>651500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1252900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-225500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1924500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>827300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1040200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-88000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1731600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>712600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>134300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>466500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1424900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>620100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>788100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>138400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1116100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>624300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>287000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>205600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1218100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>895800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>588900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-164100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1324000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>414400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-530200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-135200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-879400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-640400</v>
       </c>
-      <c r="G91" s="3">
-        <v>-422800</v>
-      </c>
       <c r="H91" s="3">
+        <v>-423700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-167000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-611100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-567700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-421600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-193800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-696200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-503900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-332600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-141000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8693900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6219400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4037300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2353100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7841100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5992400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-234300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-127300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-335800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-227600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-151900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-112900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-305600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-338500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-371300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-159500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-326900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-235600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-197400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-99100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-348500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-230500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-197600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-124700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1019300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-242200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-486400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-110700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-847700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-611600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-374900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-135600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-567900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-516700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-345500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-137000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-637400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-508900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-350600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-227900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-391300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-271900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-223700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-238500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-419500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-306300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-218000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-139900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-308800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-207200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-123600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-176300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-284400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-320700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-365900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-203400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-301200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-206200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-140400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-89100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-314300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-171700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>866900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-178000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-247400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-218600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,52 +10455,53 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>1235800</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>976000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>375100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>743300</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10279,11 +10513,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1655500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -10291,61 +10525,64 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1319200</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-230400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-463400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-503600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-802500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-284900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-504800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-225700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-361100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-148100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-473200</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-142700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1470600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-124800</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-568100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-128200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-425800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-195400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1866700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-426800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-250200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-250400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1948800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-161100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-166900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-180300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2209900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-165300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-912800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-147500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1676000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-137400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-147500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-146600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1797900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-132100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-122800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-124900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1431400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-113200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-338800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-98100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-567400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-605800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-993300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-379800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-522400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-242800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-381700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-170000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-494500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-167100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1487600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-145400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-591300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-145500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-11700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>72600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>63400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>61800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-20700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-81300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-75300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-42700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-43200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-60500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>121700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-43900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-14200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-73000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>145300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-28400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-22500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-47900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>35500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-125900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-15100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>161600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-25600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-20500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-29400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-49100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>37700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-35300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>29600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-15600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-26900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-39900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>29200</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>116400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-366100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>149300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>450900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-615100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-577000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>260500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>185900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-551600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>284700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-90600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-46400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-281100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>228100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>808700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-465400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-321300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>366300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>651600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-317400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-134500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>372600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-350000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>336500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>511200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-303700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-591400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-465200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>263000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>126200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-197400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-88900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>473300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>541400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-93200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-527500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>503000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>39200</v>
       </c>
     </row>
